--- a/Templates/t27.xlsx
+++ b/Templates/t27.xlsx
@@ -305,7 +305,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,19 +321,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.5999"/>
-        <bgColor rgb="FFF4B183"/>
+        <bgColor rgb="FFFFC2C2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999"/>
-        <bgColor rgb="FFBDD7EE"/>
+        <fgColor rgb="FFC2C8FF"/>
+        <bgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFBC2"/>
       </patternFill>
     </fill>
     <fill>
@@ -350,32 +350,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999"/>
-        <bgColor rgb="FFBFBFBF"/>
+        <fgColor rgb="FFCCFFC2"/>
+        <bgColor rgb="FFC2F0FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.3999"/>
+        <fgColor rgb="FFFFFBC2"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC2F3"/>
+        <bgColor rgb="FFFFC2C2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2F0FF"/>
+        <bgColor rgb="FFDEEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC2C2"/>
         <bgColor rgb="FFF8CBAD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999"/>
-        <bgColor rgb="FFC5E0B4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
-        <bgColor rgb="FF9DC3E6"/>
+        <bgColor rgb="FFC2C8FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.7999"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFC2F0FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -494,7 +506,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -619,11 +631,15 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="9" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -635,15 +651,23 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -686,12 +710,12 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFDEEBF7"/>
+      <rgbColor rgb="FFFFFBC2"/>
+      <rgbColor rgb="FFC2F0FF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFBDD7EE"/>
+      <rgbColor rgb="FFC2C8FF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -701,12 +725,12 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC5E0B4"/>
-      <rgbColor rgb="FFFFD966"/>
-      <rgbColor rgb="FF9DC3E6"/>
+      <rgbColor rgb="FFDEEBF7"/>
+      <rgbColor rgb="FFCCFFC2"/>
+      <rgbColor rgb="FFFFC2C2"/>
+      <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFF4B183"/>
-      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFC2F3"/>
       <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
@@ -1289,7 +1313,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
@@ -1340,7 +1364,7 @@
       <c r="AW22" s="21"/>
       <c r="AX22" s="21"/>
     </row>
-    <row r="23" customFormat="false" ht="223" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="219.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="24" t="s">
         <v>34</v>
       </c>
@@ -1386,10 +1410,10 @@
       <c r="P23" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="Q23" s="32" t="s">
+      <c r="Q23" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="R23" s="32" t="s">
+      <c r="R23" s="31" t="s">
         <v>8</v>
       </c>
       <c r="S23" s="32" t="s">
@@ -1407,112 +1431,96 @@
       <c r="W23" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="X23" s="32" t="s">
+      <c r="X23" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="Y23" s="33" t="s">
+      <c r="Y23" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="Z23" s="33" t="s">
+      <c r="Z23" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="AA23" s="33" t="s">
+      <c r="AA23" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="AB23" s="33" t="s">
+      <c r="AB23" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="AC23" s="33" t="s">
+      <c r="AC23" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="AD23" s="33" t="s">
+      <c r="AD23" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="AE23" s="33" t="s">
+      <c r="AE23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="AF23" s="33" t="s">
+      <c r="AF23" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="AG23" s="34" t="s">
+      <c r="AG23" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="AH23" s="34" t="s">
+      <c r="AH23" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="AI23" s="34" t="s">
+      <c r="AI23" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="AJ23" s="34" t="s">
+      <c r="AJ23" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="AK23" s="34" t="s">
+      <c r="AK23" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="AL23" s="34" t="s">
+      <c r="AL23" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="AM23" s="34" t="s">
+      <c r="AM23" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="AN23" s="34" t="s">
+      <c r="AN23" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="AO23" s="35" t="s">
+      <c r="AO23" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="AP23" s="35" t="s">
+      <c r="AP23" s="38" t="s">
         <v>47</v>
       </c>
       <c r="AQ23" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="AR23" s="36" t="s">
+      <c r="AR23" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="AS23" s="36" t="s">
+      <c r="AS23" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="AT23" s="37" t="s">
+      <c r="AT23" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="AU23" s="37" t="s">
+      <c r="AU23" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AV23" s="37" t="s">
+      <c r="AV23" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AW23" s="38" t="s">
+      <c r="AW23" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="AX23" s="38" t="s">
+      <c r="AX23" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="AY23" s="38" t="s">
+      <c r="AY23" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="AZ23" s="38" t="s">
+      <c r="AZ23" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="BA23" s="38" t="s">
+      <c r="BA23" s="41" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="0"/>
-      <c r="H24" s="0"/>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="0"/>
-      <c r="H25" s="0"/>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="0"/>
-      <c r="H26" s="0"/>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="0"/>
-      <c r="H27" s="0"/>
     </row>
     <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/Templates/t27.xlsx
+++ b/Templates/t27.xlsx
@@ -20,27 +20,96 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
-  <si>
-    <t xml:space="preserve">Выход на режим</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ч:мин</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Максимальная температура конденсации</t>
-  </si>
-  <si>
-    <t xml:space="preserve">˚С</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Минимальная температура кипения </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Минимальная температура всаса </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 дверь, со ступенькой</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="70">
+  <si>
+    <t xml:space="preserve">Данные</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мин.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Макс.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ср.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тип холодильника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 дверь, с ступеньками</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Pc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кол-во датчиков T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Ре</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Название испытания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тc фильтр Tс</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лаборант</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тe  всас.  Te</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Примечания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tcompr - Корпус компрессора  1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Начало испытания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tкд1 Вход в конденсатор ( воздух )  2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выбранный временной промежуток</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tкд2 выход из конденсатора ( воздух )  3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Время выбранного промежутка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tис1 Вход в испаритель ( воздух )  4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tис2 Выход из испарителя ( воздух )  5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Влажность в камере.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Т  в камере.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T конденсации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T кипения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Переохлаждение</t>
   </si>
   <si>
     <t xml:space="preserve">T4</t>
@@ -70,6 +139,9 @@
     <t xml:space="preserve">T22</t>
   </si>
   <si>
+    <t xml:space="preserve">Перегрев</t>
+  </si>
+  <si>
     <t xml:space="preserve">T1</t>
   </si>
   <si>
@@ -91,6 +163,9 @@
     <t xml:space="preserve">T24</t>
   </si>
   <si>
+    <t xml:space="preserve">Напор</t>
+  </si>
+  <si>
     <t xml:space="preserve">T2</t>
   </si>
   <si>
@@ -139,27 +214,6 @@
     <t xml:space="preserve">Ре</t>
   </si>
   <si>
-    <t xml:space="preserve">Тc фильтр Tс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тe  всас.  Te</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tcompr - Корпус компрессора  1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tкд1 Вход в конденсатор ( воздух )  2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tкд2 выход из конденсатора ( воздух )  3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tис1 Вход в испаритель ( воздух )  4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tис2 Выход из испарителя ( воздух )  5</t>
-  </si>
-  <si>
     <t xml:space="preserve">V </t>
   </si>
   <si>
@@ -169,12 +223,6 @@
     <t xml:space="preserve">W  </t>
   </si>
   <si>
-    <t xml:space="preserve">Влажность в камере.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Т  в камере.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Минимальная</t>
   </si>
   <si>
@@ -182,36 +230,20 @@
   </si>
   <si>
     <t xml:space="preserve">Максимальная</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T конденсации</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T кипения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Переохлаждение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Перегрев</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Напор</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="[h]:mm:ss"/>
     <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="[h]:mm:ss;@"/>
-    <numFmt numFmtId="167" formatCode="\+#,##0.0;\-#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="[h]:mm;@"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="[h]:mm;@"/>
+    <numFmt numFmtId="167" formatCode="0.00"/>
+    <numFmt numFmtId="168" formatCode="[h]:mm:ss;@"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,8 +284,8 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -261,9 +293,9 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
@@ -296,27 +328,13 @@
       <family val="1"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -391,7 +409,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -404,6 +422,13 @@
       <right style="medium"/>
       <top style="medium"/>
       <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -516,39 +541,35 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -559,14 +580,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -591,19 +612,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -615,15 +640,23 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -631,43 +664,35 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="9" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -930,691 +955,762 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B7:BA1048576"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:BA38"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="14.15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.25"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.42"/>
   </cols>
   <sheetData>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+    <row r="2" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="4" t="n">
-        <f aca="false">B27</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <f aca="false">MAX(AW24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
+      <c r="K2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <f aca="false">MIN(AX24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <f aca="false">MIN(H24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="3" t="str">
-        <f aca="false">IFERROR(
-IF(#REF!=[1]списки!$a$1,"",
-IF(OR(#REF!=[1]списки!$a$2,#REF!=[1]списки!$a$3),"чч:мм:сс",
-IF(#REF!=[1]списки!$a$4,"",
-IF(#REF!=[1]списки!$a$5,"",
-IF(#REF!=[1]списки!$a$6,"",
-IF(#REF!=[1]списки!$a$7,"чч:мм:сс",
-IF(#REF!=[1]списки!$a$9,"чч:мм:сс",
-""))))))),"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="6" t="str">
-        <f aca="false">IFERROR(
-IF(#REF!=[1]списки!$a$1,"",
-IF(AND(#REF!&lt;&gt;"нет метки temp",OR(#REF!=[1]списки!$a$2,#REF!=[1]списки!$a$3)),IFERROR(VLOOKUP("temp",A11:$A$978551,2,FALSE()),""),
-IF(#REF!=[1]списки!$a$4,"",
-IF(#REF!=[1]списки!$a$5,"",
-IF(#REF!=[1]списки!$a$6,"",
-IF(#REF!=[1]списки!$a$7,IFERROR(VLOOKUP("on",A11:$A$978551,2,FALSE()),""),
-IF(#REF!=[1]списки!$a$8,"",
-IF(#REF!=[1]списки!$a$9,IFERROR(VLOOKUP("off",A11:$A$978551,2,FALSE()),""),
-"")))))))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2" t="str">
-        <f aca="false">IFERROR(
-IF(#REF!=[1]списки!$a$1,"",
-IF(OR(#REF!=[1]списки!$a$2,#REF!=[1]списки!$a$3),"Макс. температура",
-IF(#REF!=[1]списки!$a$4,"",
-IF(#REF!=[1]списки!$a$5,"",
-IF(#REF!=[1]списки!$a$6,"",
-IF(#REF!=[1]списки!$a$7,"Маск. температура в конце теста",
-IF(#REF!=[1]списки!$a$8,"",
-IF(#REF!=[1]списки!$a$9,"Маск. температура в конце теста",
-"")))))))),"")</f>
-        <v/>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="3" t="str">
-        <f aca="false">IFERROR(
-IF(#REF!=[1]списки!$a$1,"",
-IF(OR(#REF!=[1]списки!$a$2,#REF!=[1]списки!$a$3),"°C",
-IF(#REF!=[1]списки!$a$4,"",
-IF(#REF!=[1]списки!$a$5,"",
-IF(#REF!=[1]списки!$a$6,"",
-IF(#REF!=[1]списки!$a$7,"°C",
-"")))))),"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="7" t="str">
-        <f aca="false">IFERROR(
-IF(#REF!=[1]списки!$a$1,"",
-IF(AND(#REF!&lt;&gt;"нет метки temp",OR(#REF!=[1]списки!$a$2,#REF!=[1]списки!$a$3)),IFERROR(VLOOKUP("temp",A12:$AB$978551,24,FALSE()),""),
-IF(#REF!=[1]списки!$a$4,"",
-IF(#REF!=[1]списки!$a$5,"",
-IF(#REF!=[1]списки!$a$6,"",
-IF(#REF!=[1]списки!$a$7,IFERROR(VLOOKUP("On",A12:$AB$978551,24,FALSE()),""),
-IF(#REF!=[1]списки!$a$8,"",
-IF(#REF!=[1]списки!$a$9,IFERROR(VLOOKUP("off",A12:$AB$978551,24,FALSE()),""),
-"")))))))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="str">
-        <f aca="false">IFERROR(
-IF(#REF!=[1]списки!$a$1,"",
-IF(OR(#REF!=[1]списки!$a$2,#REF!=[1]списки!$a$3),"Мин. температура",
-IF(#REF!=[1]списки!$a$4,"",
-IF(#REF!=[1]списки!$a$5,"",
-IF(#REF!=[1]списки!$a$6,"",
-IF(#REF!=[1]списки!$a$7,"Мин. температура в конце теста",
-IF(#REF!=[1]списки!$a$8,"",
-IF(#REF!=[1]списки!$a$9,"Мин. температура в конце теста",
-"")))))))),"")</f>
-        <v/>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="3" t="str">
-        <f aca="false">IFERROR(
-IF(#REF!=[1]списки!$a$1,"",
-IF(OR(#REF!=[1]списки!$a$2,#REF!=[1]списки!$a$3),"°C",
-IF(#REF!=[1]списки!$a$4,"",
-IF(#REF!=[1]списки!$a$5,"",
-IF(#REF!=[1]списки!$a$6,"",
-IF(#REF!=[1]списки!$a$7,"°C",
-"")))))),"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="7" t="str">
-        <f aca="false">IFERROR(
-IF(#REF!=[1]списки!$a$1,"",
-IF(AND(#REF!&lt;&gt;"нет метки temp",OR(#REF!=[1]списки!$a$2,#REF!=[1]списки!$a$3)),IFERROR(VLOOKUP("temp",A13:$AB$978551,23,FALSE()),""),
-IF(#REF!=[1]списки!$a$4,"",
-IF(#REF!=[1]списки!$a$5,"",
-IF(#REF!=[1]списки!$a$6,"",
-IF(#REF!=[1]списки!$a$7,IFERROR(VLOOKUP("On",A13:$AB$978551,23,FALSE()),""),
-IF(#REF!=[1]списки!$a$8,"",
-IF(#REF!=[1]списки!$a$9,IFERROR(VLOOKUP("off",A13:$AB$978551,23,FALSE()),""),
-"")))))))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="str">
-        <f aca="false">IFERROR(
-IF(#REF!=[1]списки!$a$1,"",
-IF(OR(#REF!=[1]списки!$a$2,#REF!=[1]списки!$a$3),"Средняя температура",
-IF(#REF!=[1]списки!$a$4,"",
-IF(#REF!=[1]списки!$a$5,"",
-IF(#REF!=[1]списки!$a$6,"",
-IF(#REF!=[1]списки!$a$7,"Средняя температура в конце теста",
-IF(#REF!=[1]списки!$a$8,"",
-IF(#REF!=[1]списки!$a$9,"Средняя температура в конце теста",
-"")))))))),"")</f>
-        <v/>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="3" t="str">
-        <f aca="false">IFERROR(
-IF(#REF!=[1]списки!$a$1,"",
-IF(OR(#REF!=[1]списки!$a$2,#REF!=[1]списки!$a$3),"°C",
-IF(#REF!=[1]списки!$a$4,"",
-IF(#REF!=[1]списки!$a$5,"",
-IF(#REF!=[1]списки!$a$6,"",
-IF(#REF!=[1]списки!$a$7,"°C",
-"")))))),"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="7" t="str">
-        <f aca="false">IFERROR(
-IF(#REF!=[1]списки!$a$1,"",
-IF(AND(#REF!&lt;&gt;"нет метки temp",OR(#REF!=[1]списки!$a$2,#REF!=[1]списки!$a$3)),IFERROR(VLOOKUP("temp",A14:$AB$978551,25,FALSE()),""),
-IF(#REF!=[1]списки!$a$4,"",
-IF(#REF!=[1]списки!$a$5,"",
-IF(#REF!=[1]списки!$a$6,"",
-IF(#REF!=[1]списки!$a$7,IFERROR(VLOOKUP("On",A14:$AB$978551,25,FALSE()),""),
-IF(#REF!=[1]списки!$a$8,"",
-IF(#REF!=[1]списки!$a$9,IFERROR(VLOOKUP("off",A14:$AB$978551,25,FALSE()),""),
-"")))))))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="9" t="s">
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="12"/>
-      <c r="O18" s="13" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="13" t="s">
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="T18" s="10"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="13" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="K4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="Y18" s="13" t="s">
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="11"/>
-      <c r="AB18" s="12"/>
-      <c r="AC18" s="13" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="K5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AD18" s="10"/>
-      <c r="AE18" s="11"/>
-      <c r="AF18" s="12"/>
-      <c r="AG18" s="13" t="s">
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AI18" s="13" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="K6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AJ18" s="10"/>
-      <c r="AK18" s="11"/>
-      <c r="AL18" s="12"/>
-      <c r="AM18" s="13" t="s">
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="AN18" s="10"/>
-      <c r="AO18" s="11"/>
-      <c r="AP18" s="12"/>
-      <c r="AQ18" s="13" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="K7" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K19" s="14"/>
-      <c r="L19" s="13" t="s">
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M19" s="15"/>
-      <c r="O19" s="16"/>
-      <c r="Q19" s="13" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="K8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="U19" s="13" t="s">
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+    </row>
+    <row r="9" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="W19" s="17"/>
-      <c r="Y19" s="16"/>
-      <c r="AA19" s="13" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="K9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="AC19" s="11"/>
-      <c r="AE19" s="13" t="s">
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="AG19" s="17"/>
-      <c r="AI19" s="16"/>
-      <c r="AK19" s="13" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AO19" s="13" t="s">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AQ19" s="17"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K20" s="13" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L20" s="18"/>
-      <c r="M20" s="13" t="s">
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="O20" s="13" t="s">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="13" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="T20" s="19"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="13" t="s">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="Y20" s="13" t="s">
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="11"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="13" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AD20" s="19"/>
-      <c r="AE20" s="11"/>
-      <c r="AF20" s="20"/>
-      <c r="AG20" s="13" t="s">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="12"/>
+      <c r="O19" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AI20" s="13" t="s">
+      <c r="P19" s="10"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AJ20" s="19"/>
-      <c r="AK20" s="11"/>
-      <c r="AL20" s="20"/>
-      <c r="AM20" s="13" t="s">
+      <c r="T19" s="10"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AN20" s="19"/>
-      <c r="AO20" s="11"/>
-      <c r="AP20" s="20"/>
-      <c r="AQ20" s="13" t="s">
+      <c r="Y19" s="13" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="23"/>
-      <c r="X22" s="23"/>
-      <c r="Y22" s="23"/>
-      <c r="Z22" s="23"/>
-      <c r="AA22" s="23"/>
-      <c r="AB22" s="23"/>
-      <c r="AC22" s="23"/>
-      <c r="AD22" s="23"/>
-      <c r="AE22" s="23"/>
-      <c r="AF22" s="23"/>
-      <c r="AG22" s="23"/>
-      <c r="AH22" s="23"/>
-      <c r="AI22" s="23"/>
-      <c r="AJ22" s="23"/>
-      <c r="AK22" s="23"/>
-      <c r="AL22" s="23"/>
-      <c r="AM22" s="23"/>
-      <c r="AN22" s="23"/>
-      <c r="AO22" s="21"/>
-      <c r="AP22" s="21"/>
-      <c r="AQ22" s="21"/>
-      <c r="AR22" s="21"/>
-      <c r="AS22" s="21"/>
-      <c r="AT22" s="21"/>
-      <c r="AU22" s="21"/>
-      <c r="AV22" s="21"/>
-      <c r="AW22" s="21"/>
-      <c r="AX22" s="21"/>
-    </row>
-    <row r="23" customFormat="false" ht="219.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="24" t="s">
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="11"/>
+      <c r="AB19" s="12"/>
+      <c r="AC19" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="AD19" s="10"/>
+      <c r="AE19" s="11"/>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="AI19" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="AJ19" s="10"/>
+      <c r="AK19" s="11"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="27" t="s">
+      <c r="AN19" s="10"/>
+      <c r="AO19" s="11"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G23" s="27" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="27" t="s">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I23" s="28" t="s">
+      <c r="M20" s="15"/>
+      <c r="O20" s="16"/>
+      <c r="Q20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="J23" s="29" t="s">
+      <c r="U20" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="K23" s="29" t="s">
+      <c r="W20" s="17"/>
+      <c r="Y20" s="16"/>
+      <c r="AA20" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="L23" s="30" t="s">
+      <c r="AC20" s="11"/>
+      <c r="AE20" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="M23" s="30" t="s">
+      <c r="AG20" s="17"/>
+      <c r="AI20" s="16"/>
+      <c r="AK20" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="N23" s="31" t="s">
+      <c r="AO20" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="AQ20" s="17"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="K21" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="18"/>
+      <c r="M21" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="T21" s="19"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y21" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z21" s="19"/>
+      <c r="AA21" s="11"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD21" s="19"/>
+      <c r="AE21" s="11"/>
+      <c r="AF21" s="20"/>
+      <c r="AG21" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI21" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ21" s="19"/>
+      <c r="AK21" s="11"/>
+      <c r="AL21" s="20"/>
+      <c r="AM21" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN21" s="19"/>
+      <c r="AO21" s="11"/>
+      <c r="AP21" s="20"/>
+      <c r="AQ21" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="23"/>
+      <c r="X23" s="23"/>
+      <c r="Y23" s="23"/>
+      <c r="Z23" s="23"/>
+      <c r="AA23" s="23"/>
+      <c r="AB23" s="23"/>
+      <c r="AC23" s="23"/>
+      <c r="AD23" s="23"/>
+      <c r="AE23" s="23"/>
+      <c r="AF23" s="23"/>
+      <c r="AG23" s="23"/>
+      <c r="AH23" s="23"/>
+      <c r="AI23" s="23"/>
+      <c r="AJ23" s="23"/>
+      <c r="AK23" s="23"/>
+      <c r="AL23" s="23"/>
+      <c r="AM23" s="23"/>
+      <c r="AN23" s="23"/>
+      <c r="AO23" s="21"/>
+      <c r="AP23" s="21"/>
+      <c r="AQ23" s="21"/>
+      <c r="AR23" s="21"/>
+      <c r="AS23" s="21"/>
+      <c r="AT23" s="21"/>
+      <c r="AU23" s="21"/>
+      <c r="AV23" s="21"/>
+      <c r="AW23" s="21"/>
+      <c r="AX23" s="21"/>
+    </row>
+    <row r="24" customFormat="false" ht="218.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="O23" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="P23" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q23" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="R23" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="S23" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="T23" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="U23" s="32" t="s">
+      <c r="K24" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="V23" s="32" t="s">
+      <c r="L24" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="M24" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="O24" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="P24" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q24" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="R24" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="S24" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="T24" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="U24" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="V24" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="W24" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="X24" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y24" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z24" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA24" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB24" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC24" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD24" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE24" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF24" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG24" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH24" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI24" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ24" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK24" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL24" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM24" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN24" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="AO24" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP24" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="AQ24" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR24" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="W23" s="32" t="s">
+      <c r="AS24" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="X23" s="33" t="s">
+      <c r="AT24" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="AU24" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="AV24" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="AW24" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="Y23" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z23" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA23" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB23" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC23" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD23" s="35" t="s">
+      <c r="AX24" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="AE23" s="35" t="s">
+      <c r="AY24" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="AF23" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG23" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH23" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI23" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ23" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK23" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AL23" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="AM23" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="AN23" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO23" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="AP23" s="38" t="s">
+      <c r="AZ24" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="BA24" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="AQ23" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR23" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="AS23" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="AT23" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="AU23" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="AV23" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="AW23" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="AX23" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="AY23" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="AZ23" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="BA23" s="41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="35" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="38">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="O2:T2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="O3:T3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="O4:T4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="O6:T6"/>
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="O7:T7"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="O8:T8"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:T9"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="N22:AN22"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="N23:AN23"/>
   </mergeCells>
-  <conditionalFormatting sqref="H7 H11">
+  <conditionalFormatting sqref="H2:I7 H11:I21">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F7="чч:мм:сс"</formula>
+      <formula>$F2="чч:мм:сс"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="H7:H15" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="H2:I21" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/Templates/t27.xlsx
+++ b/Templates/t27.xlsx
@@ -88,13 +88,13 @@
     <t xml:space="preserve">Tис2 Выход из испарителя ( воздух )  5</t>
   </si>
   <si>
+    <t xml:space="preserve">  V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  I</t>
+  </si>
+  <si>
     <t xml:space="preserve">  W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  V</t>
   </si>
   <si>
     <t xml:space="preserve">Влажность в камере.</t>
@@ -959,7 +959,7 @@
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="14.15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.25"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.42"/>
   </cols>
   <sheetData>
